--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5388,7 +5388,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5400,7 +5400,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5455,7 +5455,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5465,9 +5465,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -5481,7 +5489,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -5492,7 +5504,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5559,7 +5571,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5581,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -5581,7 +5597,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5598,13 +5618,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5655,8 +5675,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -5787,13 +5815,13 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5805,7 +5833,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5854,7 +5882,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5864,10 +5892,22 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -5884,7 +5924,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5895,13 +5939,13 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5913,7 +5957,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -5962,7 +6006,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5972,10 +6016,22 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -5992,7 +6048,11 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -6009,13 +6069,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -6066,8 +6126,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
@@ -11004,7 +11072,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -11016,7 +11084,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -11071,7 +11139,7 @@
       <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11081,9 +11149,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -11097,7 +11173,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
-      <c r="N98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -11108,7 +11188,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -11175,7 +11255,7 @@
       <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11265,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -11197,7 +11281,11 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -11214,13 +11302,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11271,8 +11359,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -11403,13 +11499,13 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11421,7 +11517,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -11470,7 +11566,7 @@
       <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11480,10 +11576,22 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -11500,7 +11608,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11511,13 +11623,13 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11529,7 +11641,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -11578,7 +11690,7 @@
       <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11588,10 +11700,22 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -11608,7 +11732,11 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11625,13 +11753,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11682,8 +11810,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
